--- a/results/momentum_rising_2026-09-29.xlsx
+++ b/results/momentum_rising_2026-09-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A96"/>
+  <dimension ref="A1:A84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,665 +426,581 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TJGC</t>
+          <t>MTLS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EGHT</t>
+          <t>ABLV</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OUST</t>
+          <t>QTRX</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>FORM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>KLAC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>AMPH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARHS</t>
+          <t>GCL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VICR</t>
+          <t>MRNA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SILC</t>
+          <t>RENX</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TNMG</t>
+          <t>FEAM</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>PRTH</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>VICR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>MYGN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>GRAL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>YDES</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>P</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>MRAM</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SGHT</t>
+          <t>NTRA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>ASYS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TAYD</t>
+          <t>REFR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SECZ</t>
+          <t>TWAV</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>MXL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>XXI</t>
+          <t>DMAC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LSCC</t>
+          <t>BNR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QMCO</t>
+          <t>AIFA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>AAON</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>PDFS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>GGR</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BATRA</t>
+          <t>KAZR</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>COHU</t>
+          <t>CRCT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MRVI</t>
+          <t>SDEV</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>LGND</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>HQI</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IMOS</t>
+          <t>SECZ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>SILC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MREO</t>
+          <t>SVRN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QTRX</t>
+          <t>SHPH</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DGII</t>
+          <t>NNBR</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>SGHT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BHFAM</t>
+          <t>PSIG</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>ARQQ</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SAIH</t>
+          <t>SXTP</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ARQQ</t>
+          <t>XXI</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>KBSX</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GLND</t>
+          <t>TAYD</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>EEIQ</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>HLP</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>MKTW</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>QMCO</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AIXC</t>
+          <t>TKNO</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>DDOG</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BLFS</t>
+          <t>OESX</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MRAM</t>
+          <t>LTRX</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GGR</t>
+          <t>WSHP</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AIFA</t>
+          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BATRK</t>
+          <t>JWEL</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SONO</t>
+          <t>ILMN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>AMRX</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>RGEN</t>
+          <t>SUIG</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>MQ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MASS</t>
+          <t>LRCX</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KBSX</t>
+          <t>COHU</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>USDE</t>
+          <t>MREO</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MLCI</t>
+          <t>EMBC</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MLCI</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>CLMB</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STKE</t>
+          <t>MASS</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KLIC</t>
+          <t>RGEN</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>OLLI</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>REFR</t>
+          <t>AGEN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>WSHP</t>
+          <t>ARHS</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>USDEW</t>
+          <t>LSCC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SDEV</t>
+          <t>BAND</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>KMTS</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BNR</t>
+          <t>FIRY</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SVCO</t>
+          <t>MPWR</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MXL</t>
+          <t>TER</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>KLIC</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SHPH</t>
+          <t>ENTG</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PSIG</t>
+          <t>STKE</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PRTH</t>
+          <t>USDE</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TKNO</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>SXTP</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>KAZR</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>SUIG</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>LTRX</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>BLLN</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>FORM</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>ABLV</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>EEIQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>MRNA</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>DMAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>ONCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>SVRN</t>
+          <t>TJGC</t>
         </is>
       </c>
     </row>
